--- a/kanban_system/output/library_linked/巴基斯坦汽车法规清单.xlsx
+++ b/kanban_system/output/library_linked/巴基斯坦汽车法规清单.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="巴基斯坦" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="巴基斯坦" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/kanban_system/output/library_linked/巴基斯坦汽车法规清单.xlsx
+++ b/kanban_system/output/library_linked/巴基斯坦汽车法规清单.xlsx
@@ -4794,6 +4794,11 @@
           <t>巴基斯坦于2020-04-24以E-64编号成为UNECE 1958协议缔约方。双轨采纳：(1)进口车辆——EDB Notification EDB/Auto/Import/WP-29/2025(2025-09-30)采纳全部62项WP-29法规，立即生效；(2)本地制造车辆——属于EDB Notification EDB/Auto/Policy/WP-29/2025(2025-09-30)第1条新增的45项WP-29法规之一，本地制造车辆须于2026-06-30前合规；如确因新技术、大额资本投入或其他困难无法按期合规，可向EDB申请最多2年延期，工业生产部可再追加1年。EDB采纳的本法规任何后续修订自动适用。</t>
         </is>
       </c>
+      <c r="Z39" s="14" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
@@ -5671,6 +5676,11 @@
           <t>巴基斯坦于2020-04-24以E-64编号成为UNECE 1958协议缔约方。双轨采纳：(1)进口车辆——EDB Notification EDB/Auto/Import/WP-29/2025(2025-09-30)采纳全部62项WP-29法规，立即生效；(2)本地制造车辆——属于EDB Notification EDB/Auto/Policy/WP-29/2025(2025-09-30)第5条确认的17项已通过SRO 656(I)/2006落地生效的WP-29法规之一，依AIDEP 2021-26本地制造车辆须于2024-06-30前全面合规。EDB采纳的本法规任何后续修订自动适用。</t>
         </is>
       </c>
+      <c r="Z47" s="14" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
@@ -5782,7 +5792,7 @@
       </c>
       <c r="Z48" s="14" t="inlineStr">
         <is>
-          <t>INS-2026-019 巴西认证为何混合联合国、美国法规？ECE、UN R、CONTRAN与RESOLUTION的区别</t>
+          <t>INS-2026-019 巴西认证为何混合联合国、美国法规？ECE、UN R、CONTRAN与RESOLUTION的区别 ; INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
         </is>
       </c>
     </row>
